--- a/SteeringCommittee_Slides17-19_Tables.xlsx
+++ b/SteeringCommittee_Slides17-19_Tables.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Slide 17 – Public Safety" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slide 18 – Criticality" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Slide 19 – Feasibility+Value" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scoring Rubric" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -552,7 +550,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Public Safety and Co-benefits</t>
+          <t>Slide 17 — Public Safety and Co-benefits</t>
         </is>
       </c>
     </row>
@@ -701,498 +699,414 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Slide 18 — Criticality</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Does the project address a critical asset identified in the Vulnerability Assessment?</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Yes, high-ranked asset</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Yes – medium risk asset</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Yes – low risk asset</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Asset not in VA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Is the project considered a critical facility/infrastructure by the LMS / does the project protect a critical facility?</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Yes, project is directly associated with a critical facility</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Project directly protects a critical facility</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Project indirectly protects critical facility (is in the general area, can have benefit)</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Project is not associated with LMS-identified critical facility/infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Does the project mitigate damages to a NFIP-identified repetitive loss structure?</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Project mitigates damage to &gt;10 NFIP-identified repetitive loss structures</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Project mitigates damage to 10&gt;x&gt;5</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Project mitigates damage for 5 or fewer repetitive loss structures</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Project does not mitigate damages for NFIP-identified repetitive loss structures</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Does this project mitigate a historical building(s), infrastructure, or system(s) that are historical or located within an official historical district or area?</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Dependency of protection for additional assets</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Slide 19 — Feasibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="75" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Is your Project identified in any current Escambia County, City of Pensacola, Town of Century, or any other organizational, governmental, for-profit, non-profit, or other community planning document?</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19" ht="75" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Shovel-Readiness – Construction
+Shovel-Readiness – Planning</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Project is fully designed and can (with funding) begin construction within the year</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Project is partially designed</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Project is named but requires complete design (concept/detail)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Project is brand new and requires extensive modeling/design</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Community Rating System (CRS): Is the project an activity that will earn credit points in one or all of the local community CRS programs?</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Earns points in all categories</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Earns points in multiple categories</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Earns points in 1 category</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>No points</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>What is the life expectancy of the project?</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>50+ years</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>25–50 years</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>10–25 years</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>0–10 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="75" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>What is the likelihood of this being grant funded?</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Most likely</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Less likely</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="75" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Is the project within an officially designated Community Redevelopment District?</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Total Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Slide 19 — Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="75" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Magnitude of flood protection</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>100-year or greater</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>50-year</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>25-year</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>&lt;25-year</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="75" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Project is important to community (community expressed interest/desire for project)</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Yes – strong community support</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Yes – moderate community support</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>No – minimal community interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Slide 19 — Cost-Benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="75" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Cost-benefit value</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>&gt;1</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Total Score</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="10">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Criterion / Question</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Score: 12</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Score: 6</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Score: 2</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Score: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Criticality</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="75" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Does the project address a critical asset identified in the Vulnerability Assessment?</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Yes, high-ranked asset</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Yes – medium risk asset</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Yes – low risk asset</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Asset not in VA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="75" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Is the project considered a critical facility/infrastructure by the LMS / does the project protect a critical facility?</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Yes, project is directly associated with a critical facility</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Project directly protects a critical facility</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Project indirectly protects critical facility (is in the general area, can have benefit)</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Project is not associated with LMS-identified critical facility/infrastructure</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Does the project mitigate damages to a NFIP-identified repetitive loss structure?</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Project mitigates damage to &gt;10 NFIP-identified repetitive loss structures</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Project mitigates damage to 10&gt;x&gt;5</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Project mitigates damage for 5 or fewer repetitive loss structures</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Project does not mitigate damages for NFIP-identified repetitive loss structures</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Does this project mitigate a historical building(s), infrastructure, or system(s) that are historical or located within an official historical district or area?</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7" ht="75" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Dependency of protection for additional assets</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total Score</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A8:E8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Criterion / Question</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Score: 12</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Score: 6</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Score: 2</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Score: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Feasibility</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="75" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Is your Project identified in any current Escambia County, City of Pensacola, Town of Century, or any other organizational, governmental, for-profit, non-profit, or other community planning document?</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr"/>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4" ht="75" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Shovel-Readiness – Construction
-Shovel-Readiness – Planning</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Project is fully designed and can (with funding) begin construction within the year</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Project is partially designed</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Project is named but requires complete design (concept/detail)</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Project is brand new and requires extensive modeling/design</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Community Rating System (CRS): Is the project an activity that will earn credit points in one or all of the local community CRS programs?</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Earns points in all categories</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Earns points in multiple categories</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Earns points in 1 category</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>No points</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>What is the life expectancy of the project?</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>50+ years</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>25–50 years</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>10–25 years</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>0–10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>What is the likelihood of this being grant funded?</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Most likely</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Likely</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Less likely</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Is the project within an officially designated Community Redevelopment District?</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="75" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Magnitude of flood protection</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>100-year or greater</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>50-year</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>25-year</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>&lt;25-year</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="75" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Project is important to community (community expressed interest/desire for project)</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr"/>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Yes – strong community support</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Yes – moderate community support</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>No – minimal community interest</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Cost-Benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Cost-benefit value</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>&gt;1</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>&lt;1</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Total Score</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A14:E14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>